--- a/artfynd/A 7643-2026 artfynd.xlsx
+++ b/artfynd/A 7643-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1512511</v>
+        <v>103591</v>
       </c>
       <c r="B2" t="n">
-        <v>89794</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5321</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588430.1345659102</v>
+        <v>588430</v>
       </c>
       <c r="R2" t="n">
-        <v>6665135.119893565</v>
+        <v>6665135</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2007-11-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1274479</v>
+        <v>139990</v>
       </c>
       <c r="B3" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4660</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588430.1345659102</v>
+        <v>588430</v>
       </c>
       <c r="R3" t="n">
-        <v>6665135.119893565</v>
+        <v>6665135</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -864,19 +844,9 @@
           <t>2007-11-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1884667</v>
+        <v>1274479</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>4660</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588430.1345659102</v>
+        <v>588430</v>
       </c>
       <c r="R4" t="n">
-        <v>6665135.119893565</v>
+        <v>6665135</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -980,19 +945,9 @@
           <t>2007-11-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103591</v>
+        <v>1512511</v>
       </c>
       <c r="B5" t="n">
-        <v>89652</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588430.1345659102</v>
+        <v>588430</v>
       </c>
       <c r="R5" t="n">
-        <v>6665135.119893565</v>
+        <v>6665135</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1096,19 +1046,9 @@
           <t>2007-11-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>139990</v>
+        <v>1884667</v>
       </c>
       <c r="B6" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>366</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588430.1345659102</v>
+        <v>588430</v>
       </c>
       <c r="R6" t="n">
-        <v>6665135.119893565</v>
+        <v>6665135</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1212,19 +1147,9 @@
           <t>2007-11-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2007-11-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 7643-2026 artfynd.xlsx
+++ b/artfynd/A 7643-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103591</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/139990</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1274479</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1512511</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,8 +1202,20 @@
           <t>Länsstyrelsen Västmanland, naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1884667</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>